--- a/experiments/completed_experiments/lysine_202504291748/protocol/hamilton/runlist.xlsx
+++ b/experiments/completed_experiments/lysine_202504291748/protocol/hamilton/runlist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/lysine_202504291748/protocol/hamilton/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/danbru_chalmers_se/Documents/Desktop/GenExp/experiments/completed_experiments/lysine_202504291748/protocol/hamilton/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_EC970FC0068F972F7984B2D7BF55DFC79091C1AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4A490EE-D150-9048-AF15-5FCC90B599DC}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_EC970FC0068F972F7984B2D7BF55DFC79091C1AC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91267329-639D-5F4D-B900-CE6D6112565A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="11" sheetId="11" r:id="rId11"/>
     <sheet name="12" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="0" concurrentCalc="0"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -464,6 +464,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -754,6 +758,7 @@
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="67.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
